--- a/SpecialResearch/wwwroot/files/Заполненная заявка.xlsx
+++ b/SpecialResearch/wwwroot/files/Заполненная заявка.xlsx
@@ -1,35 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11213"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Max/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13E7F9A8-CFE8-D447-8D3C-C06233B732A3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27320" windowHeight="15360" xr2:uid="{2CAA287F-74CE-D147-AE28-1213C2724A1C}"/>
+    <workbookView windowWidth="25200" windowHeight="12195"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Сюда введите номер заявки</t>
+  </si>
   <si>
     <t>Номер заявки</t>
   </si>
   <si>
+    <t>rrrr</t>
+  </si>
+  <si>
     <t>Оборудование</t>
   </si>
   <si>
@@ -45,68 +40,407 @@
     <t>Режим работы</t>
   </si>
   <si>
-    <t>Сюда введите номер заявки</t>
+    <t>Количество оборудования посчитается само.</t>
+  </si>
+  <si>
+    <t>Системный блок</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Монитор</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>Flatron</t>
+  </si>
+  <si>
+    <t>1280x1024x60</t>
+  </si>
+  <si>
+    <t>DVD</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Запись-чтение</t>
   </si>
   <si>
     <t>Сюда впишите всеё оборудование которое должно быть в заявке</t>
-  </si>
-  <si>
-    <t>Количество оборудования посчитается само.</t>
-  </si>
-  <si>
-    <t>Системный блок</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Монитор</t>
-  </si>
-  <si>
-    <t>LG</t>
-  </si>
-  <si>
-    <t>Flatron</t>
-  </si>
-  <si>
-    <t>1280x1024x60</t>
-  </si>
-  <si>
-    <t>DVD</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Запись-чтение</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -130,18 +464,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color theme="1"/>
-      </left>
-      <right style="thick">
-        <color theme="1"/>
-      </right>
-      <top style="thick">
-        <color theme="1"/>
+      <left style="hair">
+        <color theme="0"/>
+      </left>
+      <right style="hair">
+        <color theme="0"/>
+      </right>
+      <top style="hair">
+        <color theme="0"/>
       </top>
-      <bottom style="thick">
-        <color theme="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -154,161 +486,6 @@
       </top>
       <bottom style="hair">
         <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color theme="0"/>
-      </right>
-      <top style="hair">
-        <color theme="0"/>
-      </top>
-      <bottom style="hair">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="0"/>
-      </left>
-      <right style="hair">
-        <color theme="0"/>
-      </right>
-      <top style="hair">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thick">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thick">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thick">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -352,6 +529,60 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="hair">
         <color theme="0"/>
       </left>
@@ -363,6 +594,51 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="hair">
         <color theme="0"/>
       </left>
@@ -375,97 +651,441 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color theme="0"/>
+      </right>
+      <top style="hair">
+        <color theme="0"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="20% — Акцент3" xfId="1" builtinId="38"/>
+    <cellStyle name="Денежный [0]" xfId="2" builtinId="7"/>
+    <cellStyle name="40% — Акцент5" xfId="3" builtinId="47"/>
+    <cellStyle name="Хороший" xfId="4" builtinId="26"/>
+    <cellStyle name="Запятая [0]" xfId="5" builtinId="6"/>
+    <cellStyle name="Денежный" xfId="6" builtinId="4"/>
+    <cellStyle name="Запятая" xfId="7" builtinId="3"/>
+    <cellStyle name="40% — Акцент6" xfId="8" builtinId="51"/>
+    <cellStyle name="Процент" xfId="9" builtinId="5"/>
+    <cellStyle name="20% — Акцент2" xfId="10" builtinId="34"/>
+    <cellStyle name="Итого" xfId="11" builtinId="25"/>
+    <cellStyle name="Вывод" xfId="12" builtinId="21"/>
+    <cellStyle name="Гиперссылка" xfId="13" builtinId="8"/>
+    <cellStyle name="40% — Акцент4" xfId="14" builtinId="43"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="15" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="16" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="17" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="18" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="19" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="20" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="21" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="22" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="23" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="24" builtinId="20"/>
+    <cellStyle name="Проверить ячейку" xfId="25" builtinId="23"/>
+    <cellStyle name="Вычисление" xfId="26" builtinId="22"/>
+    <cellStyle name="Связанная ячейка" xfId="27" builtinId="24"/>
+    <cellStyle name="Плохой" xfId="28" builtinId="27"/>
+    <cellStyle name="Акцент5" xfId="29" builtinId="45"/>
+    <cellStyle name="Нейтральный" xfId="30" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="32" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="33" builtinId="31"/>
+    <cellStyle name="20% — Акцент5" xfId="34" builtinId="46"/>
+    <cellStyle name="60% — Акцент1" xfId="35" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="36" builtinId="33"/>
+    <cellStyle name="40% — Акцент2" xfId="37" builtinId="35"/>
+    <cellStyle name="20% — Акцент6" xfId="38" builtinId="50"/>
+    <cellStyle name="60% — Акцент2" xfId="39" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="40" builtinId="37"/>
+    <cellStyle name="40% — Акцент3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="42" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="43" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="44" builtinId="42"/>
+    <cellStyle name="60% — Акцент4" xfId="45" builtinId="44"/>
+    <cellStyle name="60% — Акцент5" xfId="46" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="47" builtinId="49"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -479,21 +1099,15 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
+    <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Скругленная соединительная линия 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A30BBC0-93DE-E248-8DAC-13A9400F456A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Скругленная соединительная линия 2"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1016000" y="977900"/>
-          <a:ext cx="1257300" cy="673100"/>
+          <a:off x="1016000" y="952500"/>
+          <a:ext cx="1257300" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector3">
           <a:avLst/>
@@ -532,21 +1146,15 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
+    <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="Скругленная соединительная линия 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58FCC8F8-A6EB-1B41-8C6E-AD48057E0063}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="9" name="Скругленная соединительная линия 8"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="5245100" y="393700"/>
-          <a:ext cx="711200" cy="368300"/>
+          <a:off x="5245100" y="390525"/>
+          <a:ext cx="711200" cy="333375"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector3">
           <a:avLst/>
@@ -585,21 +1193,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
+    <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Скругленная соединительная линия 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EADEA6D-C981-F545-9308-49A6D91C0E22}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="11" name="Скругленная соединительная линия 10"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1244600" y="4064000"/>
-          <a:ext cx="1485900" cy="952500"/>
+          <a:off x="1244600" y="3559175"/>
+          <a:ext cx="1485900" cy="942975"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector3">
           <a:avLst/>
@@ -671,7 +1273,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -704,26 +1306,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -756,23 +1341,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -914,75 +1482,72 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23004A0F-F344-4941-99A8-67C7F0DEE0AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A2:I32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="2"/>
-    <col min="3" max="3" width="13" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="2"/>
-    <col min="7" max="7" width="15.1640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.1640625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="13.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.8333333333333" style="1"/>
+    <col min="3" max="3" width="13" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.8333333333333" style="1"/>
+    <col min="7" max="7" width="15.1666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.8333333333333" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="19" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="1"/>
+    <row r="2" ht="32.25" spans="4:7">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="G2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1" spans="3:8">
+      <c r="C3" s="3"/>
       <c r="D3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" ht="19" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="22">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" ht="19" customHeight="1" spans="3:9">
+      <c r="C4" s="6">
         <f>COUNTA(D5:D31)</f>
         <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" spans="1:9" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:9">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="11" t="s">
         <v>9</v>
       </c>
@@ -996,11 +1561,11 @@
         <v>1455</v>
       </c>
       <c r="H5" s="13"/>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="14"/>
-      <c r="C6" s="6"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="15" t="s">
         <v>11</v>
       </c>
@@ -1016,11 +1581,11 @@
       <c r="H6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="14"/>
-      <c r="C7" s="6"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="15" t="s">
         <v>15</v>
       </c>
@@ -1036,245 +1601,246 @@
       <c r="H7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="14"/>
-      <c r="C8" s="6"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I8" s="22"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="18"/>
-      <c r="C9" s="6"/>
+      <c r="C9" s="10"/>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C10" s="6"/>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="3:9">
+      <c r="C10" s="10"/>
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C11" s="6"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="3:9">
+      <c r="C11" s="10"/>
       <c r="D11" s="15"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
       <c r="H11" s="17"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C12" s="6"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="3:9">
+      <c r="C12" s="10"/>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
       <c r="H12" s="17"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C13" s="6"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="3:9">
+      <c r="C13" s="10"/>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C14" s="6"/>
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" spans="3:9">
+      <c r="C14" s="10"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="17"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C15" s="6"/>
+      <c r="I14" s="22"/>
+    </row>
+    <row r="15" spans="3:9">
+      <c r="C15" s="10"/>
       <c r="D15" s="15"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
       <c r="H15" s="17"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C16" s="6"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="3:9">
+      <c r="C16" s="10"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
       <c r="H16" s="17"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="6"/>
+      <c r="I16" s="22"/>
+    </row>
+    <row r="17" ht="17" customHeight="1" spans="1:9">
+      <c r="A17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="10"/>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
       <c r="H17" s="17"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I17" s="22"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="14"/>
-      <c r="C18" s="6"/>
+      <c r="C18" s="10"/>
       <c r="D18" s="15"/>
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I18" s="22"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="14"/>
-      <c r="C19" s="6"/>
+      <c r="C19" s="10"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="17"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I19" s="22"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="14"/>
-      <c r="C20" s="6"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="17"/>
-      <c r="I20" s="9"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="14"/>
-      <c r="C21" s="6"/>
+      <c r="C21" s="10"/>
       <c r="D21" s="15"/>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="17"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I21" s="22"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="14"/>
-      <c r="C22" s="6"/>
+      <c r="C22" s="10"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="17"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="14"/>
-      <c r="C23" s="6"/>
+      <c r="C23" s="10"/>
       <c r="D23" s="15"/>
       <c r="E23" s="16"/>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
       <c r="H23" s="17"/>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="14"/>
-      <c r="C24" s="6"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="15"/>
       <c r="E24" s="16"/>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
       <c r="H24" s="17"/>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I24" s="22"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="14"/>
-      <c r="C25" s="6"/>
+      <c r="C25" s="10"/>
       <c r="D25" s="15"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="17"/>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I25" s="22"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="18"/>
-      <c r="C26" s="6"/>
+      <c r="C26" s="10"/>
       <c r="D26" s="15"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
       <c r="H26" s="17"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C27" s="6"/>
+      <c r="I26" s="22"/>
+    </row>
+    <row r="27" spans="3:9">
+      <c r="C27" s="10"/>
       <c r="D27" s="15"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
-      <c r="I27" s="9"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C28" s="6"/>
+      <c r="I27" s="22"/>
+    </row>
+    <row r="28" spans="3:9">
+      <c r="C28" s="10"/>
       <c r="D28" s="15"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
       <c r="H28" s="17"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C29" s="6"/>
+      <c r="I28" s="22"/>
+    </row>
+    <row r="29" spans="3:9">
+      <c r="C29" s="10"/>
       <c r="D29" s="15"/>
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
       <c r="H29" s="17"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C30" s="6"/>
+      <c r="I29" s="22"/>
+    </row>
+    <row r="30" spans="3:9">
+      <c r="C30" s="10"/>
       <c r="D30" s="15"/>
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="17"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="6"/>
+      <c r="I30" s="22"/>
+    </row>
+    <row r="31" ht="16.5" spans="3:9">
+      <c r="C31" s="10"/>
       <c r="D31" s="19"/>
       <c r="E31" s="20"/>
       <c r="F31" s="20"/>
       <c r="G31" s="20"/>
       <c r="H31" s="21"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+      <c r="I31" s="22"/>
+    </row>
+    <row r="32" ht="16.5"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:A9"/>
     <mergeCell ref="A17:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>